--- a/artfynd/A 63835-2023 artfynd.xlsx
+++ b/artfynd/A 63835-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63835-2023 artfynd.xlsx
+++ b/artfynd/A 63835-2023 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>114057106</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1030,11 +1030,11 @@
         <v>119426990</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/artfynd/A 63835-2023 artfynd.xlsx
+++ b/artfynd/A 63835-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>114057106</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>119426990</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
